--- a/Codes_2025/Trial 3/Trial3_Proposed (Weighted)_Leaders_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_Proposed (Weighted)_Leaders_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
         <v>99.25285121909999</v>
       </c>
       <c r="F2" t="n">
-        <v>80.83197021484375</v>
+        <v>83.33993530273438</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,23 +504,23 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>82.68658388390563</v>
+        <v>88.16020411342721</v>
       </c>
       <c r="I2" t="n">
-        <v>13.15658388390555</v>
+        <v>18.63020411342714</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>37.67999999999999</v>
+        <v>37.81</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50.54610131507693</v>
+        <v>37.22033627553438</v>
       </c>
       <c r="F3" t="n">
-        <v>42.97403335571289</v>
+        <v>58.80014801025391</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>43.73638889871093</v>
+        <v>52.26328864442817</v>
       </c>
       <c r="I3" t="n">
-        <v>6.056388898710935</v>
+        <v>14.45328864442817</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>37.58000000000002</v>
+        <v>37.67999999999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25.1977926501113</v>
+        <v>50.54610131507693</v>
       </c>
       <c r="F4" t="n">
-        <v>54.01039123535156</v>
+        <v>38.05873489379883</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -574,23 +574,23 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>51.10953979588824</v>
+        <v>41.8413516816042</v>
       </c>
       <c r="I4" t="n">
-        <v>13.52953979588822</v>
+        <v>4.161351681604209</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>35.4</v>
+        <v>37.58000000000002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54.79771450242716</v>
+        <v>25.1977926501113</v>
       </c>
       <c r="F5" t="n">
-        <v>43.84534072875977</v>
+        <v>53.2140007019043</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,23 +609,23 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>44.94802534545236</v>
+        <v>44.7274571560384</v>
       </c>
       <c r="I5" t="n">
-        <v>9.548025345452366</v>
+        <v>7.147457156038378</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>22.34</v>
+        <v>35.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21.49547930685887</v>
+        <v>54.79771450242716</v>
       </c>
       <c r="F6" t="n">
-        <v>22.31783294677734</v>
+        <v>50.69497299194336</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -644,23 +644,23 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>22.23503841045505</v>
+        <v>51.93775696976737</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1049615895449456</v>
+        <v>16.53775696976737</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>21.01</v>
+        <v>24.26000000000001</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22.46325384117893</v>
+        <v>36.70529760187497</v>
       </c>
       <c r="F7" t="n">
-        <v>23.52659797668457</v>
+        <v>29.90799522399902</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -679,23 +679,23 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>23.41954052551435</v>
+        <v>31.96700344229965</v>
       </c>
       <c r="I7" t="n">
-        <v>2.409540525514352</v>
+        <v>7.707003442299648</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>20.08</v>
+        <v>22.34</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14.5973875851344</v>
+        <v>21.49547930685887</v>
       </c>
       <c r="F8" t="n">
-        <v>15.0074291229248</v>
+        <v>16.00368309020996</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>14.96614615493356</v>
+        <v>17.66723326271912</v>
       </c>
       <c r="I8" t="n">
-        <v>5.113853845066437</v>
+        <v>4.672766737280881</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>10.19</v>
+        <v>21.01</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8.511111330196202</v>
+        <v>22.46325384117893</v>
       </c>
       <c r="F9" t="n">
-        <v>8.766188621520996</v>
+        <v>20.50921440124512</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -749,23 +749,23 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8.740507448560326</v>
+        <v>21.10112322654657</v>
       </c>
       <c r="I9" t="n">
-        <v>1.449492551439672</v>
+        <v>0.09112322654656424</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>9.359999999999999</v>
+        <v>20.08</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9.622454454199397</v>
+        <v>14.5973875851344</v>
       </c>
       <c r="F10" t="n">
-        <v>13.12283897399902</v>
+        <v>15.14009666442871</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -784,23 +784,23 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>12.77042038034474</v>
+        <v>14.97570167472656</v>
       </c>
       <c r="I10" t="n">
-        <v>3.410420380344737</v>
+        <v>5.104298325273442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.73</v>
+        <v>10.19</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.922944893692857</v>
+        <v>8.511111330196202</v>
       </c>
       <c r="F11" t="n">
-        <v>3.696324586868286</v>
+        <v>8.53935718536377</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -819,23 +819,23 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3.517780780052533</v>
+        <v>8.530801078148023</v>
       </c>
       <c r="I11" t="n">
-        <v>4.212219219947466</v>
+        <v>1.659198921851974</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>7.180000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.570951940213813</v>
+        <v>9.622454454199397</v>
       </c>
       <c r="F12" t="n">
-        <v>4.587805271148682</v>
+        <v>14.54071140289307</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -854,23 +854,23 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.686788444142392</v>
+        <v>13.05089516196266</v>
       </c>
       <c r="I12" t="n">
-        <v>2.493211555857608</v>
+        <v>3.690895161962663</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>6.590000000000001</v>
+        <v>7.73</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.058388586643492</v>
+        <v>1.922944893692857</v>
       </c>
       <c r="F13" t="n">
-        <v>8.104513168334961</v>
+        <v>4.037898063659668</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -889,45 +889,150 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.999189381253424</v>
+        <v>3.397245976082035</v>
       </c>
       <c r="I13" t="n">
-        <v>1.409189381253423</v>
+        <v>4.332754023917964</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7.180000000000001</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5.570951940213813</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.184887409210205</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5.3018323379393</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.878167662060701</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10.71820080519103</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9.387779235839844</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>9.790784544830455</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.980784544830455</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6.590000000000001</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>7.058388586643492</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7.764945507049561</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>7.550918467359752</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9609184673597513</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="n">
         <v>6.549999999999999</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>6.9664063060335</v>
       </c>
-      <c r="F14" t="n">
-        <v>7.286701679229736</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Leaders</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>7.25445435201831</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.7044543520183106</v>
+      <c r="F17" t="n">
+        <v>7.819563388824463</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>7.5611288882959</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.011128888295901</v>
       </c>
     </row>
   </sheetData>
